--- a/data/trans_camb/P32C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,97</t>
+          <t>-3,21; 1,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,89</t>
+          <t>-4,26; 0,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -1,4</t>
+          <t>-5,66; -1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,88</t>
+          <t>-3,36; 1,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 0,0</t>
+          <t>-4,59; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 12,82</t>
+          <t>-1,08; 12,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,06</t>
+          <t>-2,59; 1,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,1</t>
+          <t>-3,2; 0,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,55</t>
+          <t>-2,61; 2,65</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 128,75</t>
+          <t>-75,39; 141,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-90,77; 93,71</t>
+          <t>-100,0; 85,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 75,81</t>
+          <t>-76,49; 93,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,74</t>
+          <t>-92,7; 44,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-97,82; 250,98</t>
+          <t>-98,11; 283,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,43</t>
+          <t>-2,39; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,83</t>
+          <t>-2,25; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -1,05</t>
+          <t>-3,9; -0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,46</t>
+          <t>-4,82; -0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,12</t>
+          <t>-3,16; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 0,83</t>
+          <t>-3,9; 0,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,7</t>
+          <t>-2,36; 0,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,29</t>
+          <t>-1,95; 1,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,78</t>
+          <t>-3,25; -0,67</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,58; 124,28</t>
+          <t>-73,37; 120,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 160,93</t>
+          <t>-73,81; 169,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 77,43</t>
+          <t>-77,52; 58,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 107,99</t>
+          <t>-65,2; 115,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,04</t>
+          <t>-100,0; -8,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,77</t>
+          <t>0,38; 3,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,67</t>
+          <t>-0,88; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,35</t>
+          <t>-0,79; 2,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>-2,87; 0,0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>-2,3; 0,0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 0,0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,27</t>
+          <t>-0,91; 2,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,22</t>
+          <t>-0,07; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,93</t>
+          <t>-0,95; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,76</t>
+          <t>-0,54; 1,81</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 1389,83</t>
+          <t>-29,56; 1271,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 910,66</t>
+          <t>-26,58; 1074,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,46; 447,81</t>
+          <t>-100,0; 448,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,65; 768,03</t>
+          <t>-77,55; 676,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,45</t>
+          <t>-1,02; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,39</t>
+          <t>-2,27; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,09</t>
+          <t>-2,58; 1,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,0</t>
+          <t>-3,7; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,16</t>
+          <t>-1,67; 2,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,0</t>
+          <t>-4,17; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,06</t>
+          <t>-0,92; 2,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,26</t>
+          <t>-1,34; 1,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,65</t>
+          <t>-2,04; 0,53</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 929,86</t>
+          <t>-57,59; 1052,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 467,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 406,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 680,48</t>
+          <t>-62,88; 525,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,47; 440,26</t>
+          <t>-79,81; 455,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 420,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,05</t>
+          <t>-5,69; 0,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,33</t>
+          <t>-3,96; 2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,8</t>
+          <t>-4,07; 1,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,0</t>
+          <t>0,47; 4,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,94</t>
+          <t>-3,33; 0,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,8</t>
+          <t>-2,98; 1,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,75</t>
+          <t>-2,54; 1,94</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,65</t>
+          <t>-100,0; 63,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 164,75</t>
+          <t>-75,03; 136,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 140,01</t>
+          <t>-75,71; 141,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 113,04</t>
+          <t>-87,89; 79,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 192,4</t>
+          <t>-73,42; 164,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,62; 151,87</t>
+          <t>-65,19; 170,82</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,01</t>
+          <t>-0,52; 5,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,01</t>
+          <t>-0,65; 3,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,67</t>
+          <t>-0,81; 2,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,37</t>
+          <t>-0,49; 3,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,62</t>
+          <t>-0,96; 2,84</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,48</t>
+          <t>-1,69; 1,28</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -1,09</t>
+          <t>-9,6; -1,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,52</t>
+          <t>-7,2; 2,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,55</t>
+          <t>-7,45; 2,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -0,9</t>
+          <t>-8,39; -0,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,41</t>
+          <t>-6,23; 1,78</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,08</t>
+          <t>-5,69; 2,26</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-94,51; 273,26</t>
+          <t>-92,4; inf</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,01</t>
+          <t>-0,75; 0,95</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,55</t>
+          <t>-1,16; 0,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,01</t>
+          <t>-1,47; 0,05</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,03</t>
+          <t>-1,47; 0,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,37</t>
+          <t>-1,35; 0,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,92</t>
+          <t>-1,13; 0,96</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,51</t>
+          <t>-0,85; 0,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,27</t>
+          <t>-0,96; 0,29</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,09</t>
+          <t>-1,13; 0,14</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 69,46</t>
+          <t>-32,57; 62,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 37,29</t>
+          <t>-49,54; 39,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 4,48</t>
+          <t>-62,75; 6,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,9</t>
+          <t>-100,0; 49,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 132,08</t>
+          <t>-85,98; 110,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 193,9</t>
+          <t>-71,93; 211,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 41,85</t>
+          <t>-44,43; 40,66</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 25,16</t>
+          <t>-48,67; 26,0</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 9,12</t>
+          <t>-59,32; 11,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,82</t>
+          <t>-3,18; 2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,9</t>
+          <t>-3,99; 0,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,33</t>
+          <t>-5,61; -1,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,12</t>
+          <t>-3,42; 1,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,0</t>
+          <t>-4,52; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 12,02</t>
+          <t>-0,54; 13,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,11</t>
+          <t>-2,49; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,1</t>
+          <t>-3,21; 0,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,65</t>
+          <t>-2,32; 3,46</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>202,37%</t>
+          <t>317,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,83%</t>
+          <t>-0,87%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,39; 141,13</t>
+          <t>-73,82; 157,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,29</t>
+          <t>-100,0; 108,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 93,23</t>
+          <t>-74,43; 113,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-92,7; 44,0</t>
+          <t>-100,0; 27,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-98,11; 283,81</t>
+          <t>-100,0; 238,6</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,44</t>
+          <t>-2,27; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,81</t>
+          <t>-2,34; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,99</t>
+          <t>-3,91; -1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,47</t>
+          <t>-4,97; -0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,85</t>
+          <t>-3,23; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,74</t>
+          <t>-3,7; 1,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,55</t>
+          <t>-2,37; 0,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,16</t>
+          <t>-1,76; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,67</t>
+          <t>-3,28; -0,72</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,49%</t>
+          <t>-66,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-88,65%</t>
+          <t>-89,45%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,37; 120,47</t>
+          <t>-71,22; 132,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,81; 169,49</t>
+          <t>-73,76; 152,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 58,66</t>
+          <t>-79,47; 54,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 115,82</t>
+          <t>-66,87; 125,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,95</t>
+          <t>-100,0; -24,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,73</t>
+          <t>0,3; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,81</t>
+          <t>-0,83; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,33</t>
+          <t>-0,91; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-2,81; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,05</t>
+          <t>-0,92; 1,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,17</t>
+          <t>-0,12; 2,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,91</t>
+          <t>-0,8; 1,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,81</t>
+          <t>-0,57; 1,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 1271,79</t>
+          <t>-23,12; 1258,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 796,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 1074,32</t>
+          <t>-27,61; 1009,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 448,78</t>
+          <t>-88,1; 488,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,55; 676,68</t>
+          <t>-69,95; 820,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,52</t>
+          <t>-0,87; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,36</t>
+          <t>-2,04; 1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,15</t>
+          <t>-2,09; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,0</t>
+          <t>-3,8; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,43</t>
+          <t>-1,41; 2,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,0</t>
+          <t>-3,52; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,15</t>
+          <t>-1,03; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,34</t>
+          <t>-1,49; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,53</t>
+          <t>-1,84; 0,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-24,44%</t>
+          <t>-5,74%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-44,05%</t>
+          <t>-32,03%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 1052,64</t>
+          <t>-59,05; 1096,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 467,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 447,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 525,73</t>
+          <t>-65,06; 606,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 455,07</t>
+          <t>-79,45; 472,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 358,7</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,33</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,16</t>
+          <t>-5,68; 0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,31</t>
+          <t>-4,18; 2,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,93</t>
+          <t>-4,33; 1,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,0</t>
+          <t>0,43; 4,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,87</t>
+          <t>-3,57; 1,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,65</t>
+          <t>-2,82; 1,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,94</t>
+          <t>-2,98; 1,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-24,9%</t>
+          <t>-31,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,21%</t>
+          <t>-13,35%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,53</t>
+          <t>-100,0; 52,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 136,91</t>
+          <t>-77,31; 147,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 141,67</t>
+          <t>-77,37; 128,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-87,89; 79,59</t>
+          <t>-89,68; 111,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 164,24</t>
+          <t>-76,23; 179,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 170,82</t>
+          <t>-74,53; 141,9</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,31</t>
+          <t>-0,58; 4,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,63</t>
+          <t>-0,6; 4,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,9</t>
+          <t>-0,8; 2,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,45</t>
+          <t>-0,5; 3,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,84</t>
+          <t>-0,67; 2,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,28</t>
+          <t>-0,95; 2,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171,77%</t>
+          <t>159,33%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>162,95%</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,9</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -1,11</t>
+          <t>-9,83; -1,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 2,28</t>
+          <t>-7,41; 1,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,52</t>
+          <t>-7,6; 2,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -0,9</t>
+          <t>-8,32; -0,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,78</t>
+          <t>-6,28; 1,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,26</t>
+          <t>-5,53; 2,13</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-34,18%</t>
+          <t>-38,36%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-25,54%</t>
+          <t>-30,6%</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,4; inf</t>
+          <t>-93,47; —</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,95</t>
+          <t>-0,73; 1,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,55</t>
+          <t>-1,13; 0,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,05</t>
+          <t>-1,46; 0,03</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,04</t>
+          <t>-1,48; 0,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,37</t>
+          <t>-1,37; 0,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,96</t>
+          <t>-0,75; 1,56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,49</t>
+          <t>-0,83; 0,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,29</t>
+          <t>-0,94; 0,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,14</t>
+          <t>-0,96; 0,32</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-36,48%</t>
+          <t>-36,92%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-1,52%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-31,23%</t>
+          <t>-22,24%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 62,72</t>
+          <t>-32,44; 67,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 39,03</t>
+          <t>-48,39; 39,83</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 6,17</t>
+          <t>-62,97; 4,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,34</t>
+          <t>-100,0; 37,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 110,65</t>
+          <t>-86,14; 107,51</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 211,17</t>
+          <t>-60,57; 346,45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 40,66</t>
+          <t>-43,18; 36,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 26,0</t>
+          <t>-51,12; 23,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 11,59</t>
+          <t>-50,44; 26,15</t>
         </is>
       </c>
     </row>
